--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260826.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260826.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>聯詠科技</t>
+          <t>華碩電腦</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>10,306,000</t>
+          <t>6,022,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>3.99%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>華碩電腦</t>
+          <t>聯詠科技</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>6,022,000</t>
+          <t>10,306,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>3.92%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>4,326,353,831</t>
+          <t>4,286,965,364</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
@@ -836,24 +836,24 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>202609WTX</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>115/09台股期貨</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>32,953,000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,22 +865,22 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>202609WTX</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>115/09台股期貨</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>32,953,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
@@ -902,46 +902,46 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>34,731,000</t>
+          <t>6,624,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>6,624,000</t>
+          <t>34,731,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,39 +953,39 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>9,588,000</t>
+          <t>543,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>36,304,000</t>
+          <t>9,588,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1019,44 +1019,44 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>4,161,000</t>
+          <t>36,304,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>543,000</t>
+          <t>4,161,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -1078,51 +1078,51 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,548,000</t>
+          <t>2,845,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,845,000</t>
+          <t>9,548,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -1151,88 +1151,88 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>15,213,000</t>
+          <t>14,264,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,002,000</t>
+          <t>41,037,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>41,037,000</t>
+          <t>18,002,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14,264,000</t>
+          <t>15,213,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,569,121,747</t>
+          <t>2,646,801,747</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1276,112 +1276,112 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>24,954,004</t>
+          <t>7,883,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>9,652,000</t>
+          <t>4,984,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>7,883,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>4,984,000</t>
+          <t>9,652,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>14,405,000</t>
+          <t>24,954,004</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,22 +1393,22 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>6,600,000</t>
+          <t>14,405,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1606,68 +1606,68 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,586,000</t>
+          <t>18,852,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>48,160,000</t>
+          <t>1,586,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>18,852,000</t>
+          <t>48,160,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-39,388,467</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
